--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11530,7 +11530,7 @@
         <v>46269</v>
       </c>
       <c r="B1393">
-        <v>156.266</v>
+        <v>156.014</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1393"/>
+  <dimension ref="A1:B1394"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11533,6 +11533,14 @@
         <v>156.014</v>
       </c>
     </row>
+    <row r="1394" spans="1:2">
+      <c r="A1394" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B1394">
+        <v>154.24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11538,7 +11538,7 @@
         <v>46276</v>
       </c>
       <c r="B1394">
-        <v>154.24</v>
+        <v>153.278</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11538,7 +11538,7 @@
         <v>46276</v>
       </c>
       <c r="B1394">
-        <v>153.278</v>
+        <v>154.19</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11538,7 +11538,7 @@
         <v>46276</v>
       </c>
       <c r="B1394">
-        <v>154.19</v>
+        <v>154.005</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11538,7 +11538,7 @@
         <v>46276</v>
       </c>
       <c r="B1394">
-        <v>154.005</v>
+        <v>153.515</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1394"/>
+  <dimension ref="A1:B1395"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11541,6 +11541,14 @@
         <v>153.515</v>
       </c>
     </row>
+    <row r="1395" spans="1:2">
+      <c r="A1395" s="3">
+        <v>46283</v>
+      </c>
+      <c r="B1395">
+        <v>154.927</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11546,7 +11546,7 @@
         <v>46283</v>
       </c>
       <c r="B1395">
-        <v>154.927</v>
+        <v>155.042</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11546,7 +11546,7 @@
         <v>46283</v>
       </c>
       <c r="B1395">
-        <v>155.042</v>
+        <v>155.804</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11546,7 +11546,7 @@
         <v>46283</v>
       </c>
       <c r="B1395">
-        <v>155.804</v>
+        <v>157.8075</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11546,7 +11546,7 @@
         <v>46283</v>
       </c>
       <c r="B1395">
-        <v>157.8075</v>
+        <v>156.87</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1395"/>
+  <dimension ref="A1:B1396"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11549,6 +11549,14 @@
         <v>156.87</v>
       </c>
     </row>
+    <row r="1396" spans="1:2">
+      <c r="A1396" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1396">
+        <v>157.1105</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11554,7 +11554,7 @@
         <v>46290</v>
       </c>
       <c r="B1396">
-        <v>157.1105</v>
+        <v>157.9215</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11554,7 +11554,7 @@
         <v>46290</v>
       </c>
       <c r="B1396">
-        <v>157.9215</v>
+        <v>158.8345</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11554,7 +11554,7 @@
         <v>46290</v>
       </c>
       <c r="B1396">
-        <v>158.8345</v>
+        <v>157.572</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11554,7 +11554,7 @@
         <v>46290</v>
       </c>
       <c r="B1396">
-        <v>157.572</v>
+        <v>157.2345</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1396"/>
+  <dimension ref="A1:B1397"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11557,6 +11557,14 @@
         <v>157.2345</v>
       </c>
     </row>
+    <row r="1397" spans="1:2">
+      <c r="A1397" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B1397">
+        <v>157.035</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11562,7 +11562,7 @@
         <v>46297</v>
       </c>
       <c r="B1397">
-        <v>157.035</v>
+        <v>157.031</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11562,7 +11562,7 @@
         <v>46297</v>
       </c>
       <c r="B1397">
-        <v>157.031</v>
+        <v>157.903</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11562,7 +11562,7 @@
         <v>46297</v>
       </c>
       <c r="B1397">
-        <v>157.903</v>
+        <v>157.6555</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11562,7 +11562,7 @@
         <v>46297</v>
       </c>
       <c r="B1397">
-        <v>157.6555</v>
+        <v>157.859</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1397"/>
+  <dimension ref="A1:B1398"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11565,6 +11565,14 @@
         <v>157.859</v>
       </c>
     </row>
+    <row r="1398" spans="1:2">
+      <c r="A1398" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B1398">
+        <v>158.325</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11570,7 +11570,7 @@
         <v>46304</v>
       </c>
       <c r="B1398">
-        <v>158.325</v>
+        <v>158.264</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11570,7 +11570,7 @@
         <v>46304</v>
       </c>
       <c r="B1398">
-        <v>158.264</v>
+        <v>158.238</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11570,7 +11570,7 @@
         <v>46304</v>
       </c>
       <c r="B1398">
-        <v>158.238</v>
+        <v>158.322</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1398"/>
+  <dimension ref="A1:B1399"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11573,6 +11573,14 @@
         <v>158.322</v>
       </c>
     </row>
+    <row r="1399" spans="1:2">
+      <c r="A1399" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B1399">
+        <v>158.139</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11578,7 +11578,7 @@
         <v>46311</v>
       </c>
       <c r="B1399">
-        <v>158.139</v>
+        <v>158.437</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1399"/>
+  <dimension ref="A1:B1398"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11573,14 +11573,6 @@
         <v>158.322</v>
       </c>
     </row>
-    <row r="1399" spans="1:2">
-      <c r="A1399" s="3">
-        <v>46311</v>
-      </c>
-      <c r="B1399">
-        <v>158.437</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1398"/>
+  <dimension ref="A1:B1399"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -11573,6 +11573,14 @@
         <v>158.322</v>
       </c>
     </row>
+    <row r="1399" spans="1:2">
+      <c r="A1399" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B1399">
+        <v>157.932</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDJPY_diff_0th_diff.xlsx
+++ b/public/data/files/USDJPY_diff_0th_diff.xlsx
@@ -11578,7 +11578,7 @@
         <v>46311</v>
       </c>
       <c r="B1399">
-        <v>157.932</v>
+        <v>158.0465</v>
       </c>
     </row>
   </sheetData>
